--- a/Text2SQL_Template/output/generated_datasets/ddq_autogen_transaction.xlsx
+++ b/Text2SQL_Template/output/generated_datasets/ddq_autogen_transaction.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\proton-intern\javisAI\6804_ddq\Text2SQL_Template\output\generated_datasets\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430C448E-EC72-415A-A59F-756FB4C2370E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2631" yWindow="1517" windowWidth="23195" windowHeight="12574" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -37,25 +31,25 @@
     <t>metadata</t>
   </si>
   <si>
-    <t>transaction | Tra cứu khóa chính</t>
-  </si>
-  <si>
-    <t>transaction | Tra cứu mã định danh giao dịch theo nghiệp vụ phân biệt các giao dịch với nhau</t>
-  </si>
-  <si>
-    <t>transaction | Tra cứu mã lệnh cha</t>
-  </si>
-  <si>
-    <t>transaction | Lọc thời gian theo thời điểm chính xác giao dịch phát sinh.</t>
-  </si>
-  <si>
-    <t>transaction | Lọc theo loại giao dịch hoặc nhóm giao dịch</t>
-  </si>
-  <si>
-    <t>transaction | Lọc theo nguồn nhận</t>
-  </si>
-  <si>
-    <t>transaction | Lọc theo stak người dùng loại do</t>
+    <t>transaction | Tra cứu số bút toán</t>
+  </si>
+  <si>
+    <t>transaction | Tra cứu phân biệt các giao dịch với nhau</t>
+  </si>
+  <si>
+    <t>transaction | Tra cứu số parent</t>
+  </si>
+  <si>
+    <t>transaction | Lọc thời gian theo thời điểm chính xác giao dịch phát sinh</t>
+  </si>
+  <si>
+    <t>transaction | Lọc theo loại giao dịch chi tiết hoặc mô tả nhóm giao dịch</t>
+  </si>
+  <si>
+    <t>transaction | Lọc theo kênh tiếp nhận giao dịch</t>
+  </si>
+  <si>
+    <t>transaction | Lọc theo loại người dùng tác nghiệp</t>
   </si>
   <si>
     <t>transaction | Tra cứu người dùng do</t>
@@ -64,10 +58,10 @@
     <t>transaction | Tra cứu mã yêu cầu gốc</t>
   </si>
   <si>
-    <t>transaction | Tra cứu id khách hàng chuyển tiền/người thanh toán.</t>
-  </si>
-  <si>
-    <t>transaction | Tra cứu số từ khách hàng</t>
+    <t>transaction | Tra cứu khách hàng chuyển tiền</t>
+  </si>
+  <si>
+    <t>transaction | Tra cứu customer information file</t>
   </si>
   <si>
     <t>transaction | Tra cứu mã chi nhánh quản lý khách hàng người chuyển</t>
@@ -76,103 +70,103 @@
     <t>transaction | Lọc theo hạng hoặc nhóm tài khoản nguồn</t>
   </si>
   <si>
-    <t>transaction | Lọc theo loại tài khoản nguồn</t>
-  </si>
-  <si>
-    <t>transaction | Lọc theo vnd, usd, eur...</t>
+    <t>transaction | Lọc theo loại từ tài khoản</t>
+  </si>
+  <si>
+    <t>transaction | Lọc theo từ tài khoản loại tiền</t>
   </si>
   <si>
     <t>transaction | Lọc theo từ tài khoản tên đầy đủ</t>
   </si>
   <si>
-    <t>transaction | Tra cứu số đến khách hàng</t>
-  </si>
-  <si>
-    <t>transaction | Tra cứu mã chi nhánh quản lý khách hàng thụ hưởng.</t>
+    <t>transaction | Tra cứu nếu là chuyển khoản nội bộ</t>
+  </si>
+  <si>
+    <t>transaction | Tra cứu đến khách hàng chi nhánh</t>
   </si>
   <si>
     <t>transaction | Lọc theo đến tài khoản loại tiền</t>
   </si>
   <si>
-    <t>transaction | Thống kê sau khi quy đổi tỷ giá nếu có</t>
-  </si>
-  <si>
-    <t>transaction | Thống kê số tiền giao dịch</t>
+    <t>transaction | Thống kê số tiền thực tế ghi có vào tài khoản nhận</t>
+  </si>
+  <si>
+    <t>transaction | Thống kê số tiền chuyển</t>
   </si>
   <si>
     <t>transaction | Thống kê số tiền loại tiền</t>
   </si>
   <si>
-    <t>transaction | Lọc theo số tiền lãi suất</t>
-  </si>
-  <si>
-    <t>transaction | Thống kê tiền bị giữ</t>
-  </si>
-  <si>
-    <t>transaction | Tra cứu mã tham chiếu lệnh phong tỏa tiền</t>
+    <t>transaction | Lọc theo tỷ giá quy đổi áp dụng cho giao dịch</t>
+  </si>
+  <si>
+    <t>transaction | Thống kê block số tiền</t>
+  </si>
+  <si>
+    <t>transaction | Tra cứu số trạng thái số tiền tham chiếu</t>
   </si>
   <si>
     <t>transaction | Thống kê phí affect object</t>
   </si>
   <si>
-    <t>transaction | Thống kê phí dịch vụ</t>
-  </si>
-  <si>
-    <t>transaction | Thống kê loại tiền tệ phí.</t>
-  </si>
-  <si>
-    <t>transaction | Thống kê nếu loại tiền phí khác loại tiền tài khoản</t>
-  </si>
-  <si>
-    <t>transaction | Thống kê số tiền hoa hồng trả cho đại lý/đối tác</t>
-  </si>
-  <si>
-    <t>transaction | Lọc theo hoa hồng loại tiền</t>
-  </si>
-  <si>
-    <t>transaction | Tra cứu reference number</t>
+    <t>transaction | Thống kê phí số tiền</t>
+  </si>
+  <si>
+    <t>transaction | Thống kê phí loại tiền</t>
+  </si>
+  <si>
+    <t>transaction | Thống kê phí số tiền lãi suất</t>
+  </si>
+  <si>
+    <t>transaction | Thống kê nếu có</t>
+  </si>
+  <si>
+    <t>transaction | Lọc theo loại tiền tệ hoa hồng</t>
+  </si>
+  <si>
+    <t>transaction | Tra cứu số giao dịch tham chiếu</t>
   </si>
   <si>
     <t>transaction | Lọc thời gian theo yêu cầu thời gian</t>
   </si>
   <si>
-    <t>transaction | Lọc theo yêu cầu kênh</t>
+    <t>transaction | Lọc theo tương tự channel_receiver</t>
   </si>
   <si>
     <t>transaction | Tra cứu số giao dịch revert tham chiếu</t>
   </si>
   <si>
-    <t>transaction | Lọc thời gian theo response thời gian</t>
-  </si>
-  <si>
-    <t>transaction | Lọc theo trạng thái response</t>
+    <t>transaction | Lọc thời gian theo trạng thái giờ</t>
+  </si>
+  <si>
+    <t>transaction | Lọc theo s - success</t>
   </si>
   <si>
     <t>transaction | Lọc thời gian theo thời gian duyệt giao dịch</t>
   </si>
   <si>
-    <t>transaction | Lọc thời gian theo thời gian tạo lệnh.</t>
-  </si>
-  <si>
-    <t>transaction | Lọc theo trạng thái phê duyệt</t>
+    <t>transaction | Lọc thời gian theo ngày sản phẩm</t>
+  </si>
+  <si>
+    <t>transaction | Lọc theo kết quả duyệt</t>
   </si>
   <si>
     <t>transaction | Lọc theo trạng thái cuối cùng giao dịch</t>
   </si>
   <si>
-    <t>transaction | Tra cứu ft id</t>
-  </si>
-  <si>
-    <t>transaction | Tra cứu số core revert tham chiếu</t>
-  </si>
-  <si>
-    <t>transaction | Tra cứu mã giao dịch tham chiếu tại cổng thanh toán.</t>
-  </si>
-  <si>
-    <t>transaction | Lọc theo trạng thái trả từ cổng thanh toán</t>
-  </si>
-  <si>
-    <t>transaction | Tra cứu mã hóa đơn khách hàng</t>
+    <t>transaction | Tra cứu số nội dung tham chiếu</t>
+  </si>
+  <si>
+    <t>transaction | Tra cứu số nội dung trạng thái tham chiếu</t>
+  </si>
+  <si>
+    <t>transaction | Tra cứu mã giao dịch tham chiếu cổng thanh toán</t>
+  </si>
+  <si>
+    <t>transaction | Lọc theo trạng thái trả về từ cổng thanh toán</t>
+  </si>
+  <si>
+    <t>transaction | Tra cứu số hóa đơn khách hàng</t>
   </si>
   <si>
     <t>transaction | Lọc theo loại hóa đơn</t>
@@ -181,67 +175,67 @@
     <t>transaction | Lọc theo loại tiền tệ hóa đơn</t>
   </si>
   <si>
-    <t>transaction | Lọc thời gian theo ngày hóa đơn từ</t>
+    <t>transaction | Lọc thời gian theo ngày bắt đầu kỳ cước hóa đơn</t>
   </si>
   <si>
     <t>transaction | Lọc thời gian theo ngày hóa đơn đến</t>
   </si>
   <si>
-    <t>transaction | Lọc thời gian theo thời gian bản ghi chèn vào cơ sở</t>
-  </si>
-  <si>
-    <t>transaction | Lọc thời gian theo finish thời gian</t>
-  </si>
-  <si>
-    <t>transaction | Thống kê discount số tiền</t>
-  </si>
-  <si>
-    <t>transaction | Thống kê số tiền người dùng nhập vào ban đầu</t>
-  </si>
-  <si>
-    <t>transaction | Lọc thời gian theo thời gian tiền về</t>
-  </si>
-  <si>
-    <t>transaction | Thống kê thuế vat</t>
-  </si>
-  <si>
-    <t>transaction | Thống kê số tiền chiết khấu do đối tác tài trợ.</t>
-  </si>
-  <si>
-    <t>transaction | Lọc theo loại nguồn tiền</t>
-  </si>
-  <si>
-    <t>transaction | Tra cứu mã khách hàng tác nghiệp số</t>
-  </si>
-  <si>
-    <t>transaction | Thống kê giá trị tiền ghi trên hóa đơn cần thanh toán.</t>
-  </si>
-  <si>
-    <t>transaction | Tra cứu tương tự from_cust_no nhưng thường định danh core banking</t>
+    <t>transaction | Lọc thời gian theo insert thời gian</t>
+  </si>
+  <si>
+    <t>transaction | Lọc thời gian theo thời gian kết thúc</t>
+  </si>
+  <si>
+    <t>transaction | Thống kê khuyến mãi</t>
+  </si>
+  <si>
+    <t>transaction | Thống kê nội dung số tiền</t>
+  </si>
+  <si>
+    <t>transaction | Lọc thời gian theo receive thời gian</t>
+  </si>
+  <si>
+    <t>transaction | Thống kê thường tính trên phí dịch vụ</t>
+  </si>
+  <si>
+    <t>transaction | Thống kê chiết khấu đối tác</t>
+  </si>
+  <si>
+    <t>transaction | Lọc theo ewallet - ví</t>
+  </si>
+  <si>
+    <t>transaction | Tra cứu khách hàng số do</t>
+  </si>
+  <si>
+    <t>transaction | Thống kê giá trị tiền ghi trên hóa đơn cần thanh toán</t>
+  </si>
+  <si>
+    <t>transaction | Tra cứu số từ mã khách hàng</t>
   </si>
   <si>
     <t>transaction | Lọc Loại + Số tiền</t>
   </si>
   <si>
-    <t>Tìm kiếm chính xác theo khóa chính</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo mã định danh giao dịch theo nghiệp vụ phân biệt các giao dịch với nhau</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo mã lệnh cha</t>
-  </si>
-  <si>
-    <t>Truy vấn lịch sử dựa trên cột thời điểm chính xác giao dịch phát sinh.</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo loại giao dịch hoặc nhóm giao dịch</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo nguồn nhận</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo stak người dùng loại do</t>
+    <t>Tìm kiếm chính xác theo số bút toán</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo phân biệt các giao dịch với nhau</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo số parent</t>
+  </si>
+  <si>
+    <t>Truy vấn lịch sử dựa trên cột thời điểm chính xác giao dịch phát sinh</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo loại giao dịch chi tiết hoặc mô tả nhóm giao dịch</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo kênh tiếp nhận giao dịch</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo loại người dùng tác nghiệp</t>
   </si>
   <si>
     <t>Tìm kiếm chính xác theo người dùng do</t>
@@ -250,10 +244,10 @@
     <t>Tìm kiếm chính xác theo mã yêu cầu gốc</t>
   </si>
   <si>
-    <t>Tìm kiếm chính xác theo id khách hàng chuyển tiền/người thanh toán.</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo số từ khách hàng</t>
+    <t>Tìm kiếm chính xác theo khách hàng chuyển tiền</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo customer information file</t>
   </si>
   <si>
     <t>Tìm kiếm chính xác theo mã chi nhánh quản lý khách hàng người chuyển</t>
@@ -262,103 +256,103 @@
     <t>Phân nhóm giao dịch theo hạng hoặc nhóm tài khoản nguồn</t>
   </si>
   <si>
-    <t>Phân nhóm giao dịch theo loại tài khoản nguồn</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo vnd, usd, eur...</t>
+    <t>Phân nhóm giao dịch theo loại từ tài khoản</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo từ tài khoản loại tiền</t>
   </si>
   <si>
     <t>Phân nhóm giao dịch theo từ tài khoản tên đầy đủ</t>
   </si>
   <si>
-    <t>Tìm kiếm chính xác theo số đến khách hàng</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo mã chi nhánh quản lý khách hàng thụ hưởng.</t>
+    <t>Tìm kiếm chính xác theo nếu là chuyển khoản nội bộ</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo đến khách hàng chi nhánh</t>
   </si>
   <si>
     <t>Phân nhóm giao dịch theo đến tài khoản loại tiền</t>
   </si>
   <si>
-    <t>Tính tổng giá trị sau khi quy đổi tỷ giá nếu có</t>
-  </si>
-  <si>
-    <t>Tính tổng giá trị số tiền giao dịch</t>
+    <t>Tính tổng giá trị số tiền thực tế ghi có vào tài khoản nhận</t>
+  </si>
+  <si>
+    <t>Tính tổng giá trị số tiền chuyển</t>
   </si>
   <si>
     <t>Tính tổng giá trị số tiền loại tiền</t>
   </si>
   <si>
-    <t>Phân nhóm giao dịch theo số tiền lãi suất</t>
-  </si>
-  <si>
-    <t>Tính tổng giá trị tiền bị giữ</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo mã tham chiếu lệnh phong tỏa tiền</t>
+    <t>Phân nhóm giao dịch theo tỷ giá quy đổi áp dụng cho giao dịch</t>
+  </si>
+  <si>
+    <t>Tính tổng giá trị block số tiền</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo số trạng thái số tiền tham chiếu</t>
   </si>
   <si>
     <t>Tính tổng giá trị phí affect object</t>
   </si>
   <si>
-    <t>Tính tổng giá trị phí dịch vụ</t>
-  </si>
-  <si>
-    <t>Tính tổng giá trị loại tiền tệ phí.</t>
-  </si>
-  <si>
-    <t>Tính tổng giá trị nếu loại tiền phí khác loại tiền tài khoản</t>
-  </si>
-  <si>
-    <t>Tính tổng giá trị số tiền hoa hồng trả cho đại lý/đối tác</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo hoa hồng loại tiền</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo reference number</t>
+    <t>Tính tổng giá trị phí số tiền</t>
+  </si>
+  <si>
+    <t>Tính tổng giá trị phí loại tiền</t>
+  </si>
+  <si>
+    <t>Tính tổng giá trị phí số tiền lãi suất</t>
+  </si>
+  <si>
+    <t>Tính tổng giá trị nếu có</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo loại tiền tệ hoa hồng</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo số giao dịch tham chiếu</t>
   </si>
   <si>
     <t>Truy vấn lịch sử dựa trên cột yêu cầu thời gian</t>
   </si>
   <si>
-    <t>Phân nhóm giao dịch theo yêu cầu kênh</t>
+    <t>Phân nhóm giao dịch theo tương tự channel_receiver</t>
   </si>
   <si>
     <t>Tìm kiếm chính xác theo số giao dịch revert tham chiếu</t>
   </si>
   <si>
-    <t>Truy vấn lịch sử dựa trên cột response thời gian</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo trạng thái response</t>
+    <t>Truy vấn lịch sử dựa trên cột trạng thái giờ</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo s - success</t>
   </si>
   <si>
     <t>Truy vấn lịch sử dựa trên cột thời gian duyệt giao dịch</t>
   </si>
   <si>
-    <t>Truy vấn lịch sử dựa trên cột thời gian tạo lệnh.</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo trạng thái phê duyệt</t>
+    <t>Truy vấn lịch sử dựa trên cột ngày sản phẩm</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo kết quả duyệt</t>
   </si>
   <si>
     <t>Phân nhóm giao dịch theo trạng thái cuối cùng giao dịch</t>
   </si>
   <si>
-    <t>Tìm kiếm chính xác theo ft id</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo số core revert tham chiếu</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo mã giao dịch tham chiếu tại cổng thanh toán.</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo trạng thái trả từ cổng thanh toán</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo mã hóa đơn khách hàng</t>
+    <t>Tìm kiếm chính xác theo số nội dung tham chiếu</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo số nội dung trạng thái tham chiếu</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo mã giao dịch tham chiếu cổng thanh toán</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo trạng thái trả về từ cổng thanh toán</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo số hóa đơn khách hàng</t>
   </si>
   <si>
     <t>Phân nhóm giao dịch theo loại hóa đơn</t>
@@ -367,173 +361,173 @@
     <t>Phân nhóm giao dịch theo loại tiền tệ hóa đơn</t>
   </si>
   <si>
-    <t>Truy vấn lịch sử dựa trên cột ngày hóa đơn từ</t>
+    <t>Truy vấn lịch sử dựa trên cột ngày bắt đầu kỳ cước hóa đơn</t>
   </si>
   <si>
     <t>Truy vấn lịch sử dựa trên cột ngày hóa đơn đến</t>
   </si>
   <si>
-    <t>Truy vấn lịch sử dựa trên cột thời gian bản ghi chèn vào cơ sở</t>
-  </si>
-  <si>
-    <t>Truy vấn lịch sử dựa trên cột finish thời gian</t>
-  </si>
-  <si>
-    <t>Tính tổng giá trị discount số tiền</t>
-  </si>
-  <si>
-    <t>Tính tổng giá trị số tiền người dùng nhập vào ban đầu</t>
-  </si>
-  <si>
-    <t>Truy vấn lịch sử dựa trên cột thời gian tiền về</t>
-  </si>
-  <si>
-    <t>Tính tổng giá trị thuế vat</t>
-  </si>
-  <si>
-    <t>Tính tổng giá trị số tiền chiết khấu do đối tác tài trợ.</t>
-  </si>
-  <si>
-    <t>Phân nhóm giao dịch theo loại nguồn tiền</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo mã khách hàng tác nghiệp số</t>
-  </si>
-  <si>
-    <t>Tính tổng giá trị giá trị tiền ghi trên hóa đơn cần thanh toán.</t>
-  </si>
-  <si>
-    <t>Tìm kiếm chính xác theo tương tự from_cust_no nhưng thường định danh core banking</t>
+    <t>Truy vấn lịch sử dựa trên cột insert thời gian</t>
+  </si>
+  <si>
+    <t>Truy vấn lịch sử dựa trên cột thời gian kết thúc</t>
+  </si>
+  <si>
+    <t>Tính tổng giá trị khuyến mãi</t>
+  </si>
+  <si>
+    <t>Tính tổng giá trị nội dung số tiền</t>
+  </si>
+  <si>
+    <t>Truy vấn lịch sử dựa trên cột receive thời gian</t>
+  </si>
+  <si>
+    <t>Tính tổng giá trị thường tính trên phí dịch vụ</t>
+  </si>
+  <si>
+    <t>Tính tổng giá trị chiết khấu đối tác</t>
+  </si>
+  <si>
+    <t>Phân nhóm giao dịch theo ewallet - ví</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo khách hàng số do</t>
+  </si>
+  <si>
+    <t>Tính tổng giá trị giá trị tiền ghi trên hóa đơn cần thanh toán</t>
+  </si>
+  <si>
+    <t>Tìm kiếm chính xác theo số từ mã khách hàng</t>
   </si>
   <si>
     <t>Lọc nâng cao: Loại giao dịch + Số tiền tối thiểu</t>
   </si>
   <si>
-    <t>Check khóa chính FT4763647715 giúp em
-Tìm giao dịch có khóa chính là FT4763647715
-Tra soát theo khóa chính FT4763647715</t>
-  </si>
-  <si>
-    <t>Check giao dịch FT3321797299
-Kiểm tra lệnh FT3321797299 đang ở trạng thái nào
-Xem chi tiết giao dịch số FT3321797299
-Tra cứu giao dịch FT3321797299 hôm nay</t>
-  </si>
-  <si>
-    <t>Tra soát theo mã lệnh cha 549
-Tìm giao dịch có mã lệnh cha là 549
-Check mã lệnh cha 549 giúp em</t>
-  </si>
-  <si>
-    <t>Sao kê giao dịch theo thời điểm chính xác giao dịch phát sinh. từ ngày 2026-01-14 đến ngày 2026-02-03
-Lọc giao dịch có thời điểm chính xác giao dịch phát sinh. trong khoảng 2026-01-14 - 2026-02-03
-Xem lịch sử giao dịch dựa trên thời điểm chính xác giao dịch phát sinh. từ 2026-01-14 tới 2026-02-03
-Kiểm tra các giao dịch với thời điểm chính xác giao dịch phát sinh. là ngày 2026-01-14</t>
-  </si>
-  <si>
-    <t>danh sách giao dịch chuyển liên ngân hàng
-danh sách giao dịch hóa đơn điện
-giao dịch hóa đơn điện
-danh sách giao dịch nạp thẻ
-lọc các giao dịch đang hóa đơn điện
+    <t>Tra soát theo số bút toán FT4059671687
+Check số bút toán FT4059671687 giúp em
+Tìm giao dịch có số bút toán là FT4059671687</t>
+  </si>
+  <si>
+    <t>Check giao dịch FT4451296687
+Kiểm tra lệnh FT4451296687 xem thành công chưa
+Tra cứu giao dịch FT4451296687 tuần này
+Xem chi tiết giao dịch số FT4451296687</t>
+  </si>
+  <si>
+    <t>Tìm giao dịch có số parent là 981
+Tra soát theo số parent 981
+Check số parent 981 giúp em</t>
+  </si>
+  <si>
+    <t>Sao kê giao dịch theo thời điểm chính xác giao dịch phát sinh từ ngày 2026-01-21 đến ngày 2026-02-03
+Lọc giao dịch có thời điểm chính xác giao dịch phát sinh trong khoảng 2026-01-21 - 2026-02-03
+Xem lịch sử giao dịch dựa trên thời điểm chính xác giao dịch phát sinh từ 2026-01-21 tới 2026-02-03
+Kiểm tra các giao dịch với thời điểm chính xác giao dịch phát sinh là ngày 2026-01-21</t>
+  </si>
+  <si>
+    <t>lọc các giao dịch đang thanh toán qr
+danh sách giao dịch chuyển cùng ngân hàng
+giao dịch thanh toán qr
+lọc các giao dịch đang tiền nước
+lọc các giao dịch đang chuyển cùng ngân hàng
+giao dịch tiền nước
+danh sách giao dịch tiền nước
+danh sách giao dịch thanh toán qr
+giao dịch chuyển cùng ngân hàng</t>
+  </si>
+  <si>
+    <t>lọc các giao dịch đang máy rút tiền
+giao dịch trên app
+danh sách giao dịch trên app
+lọc các giao dịch đang trên app
+giao dịch máy rút tiền
+lọc các giao dịch đang trên web
+giao dịch trên web
+danh sách giao dịch trên web
+danh sách giao dịch máy rút tiền</t>
+  </si>
+  <si>
+    <t>danh sách giao dịch chuyển cùng ngân hàng
+giao dịch tiền điện
+danh sách giao dịch chuyển liên ngân hàng
+lọc các giao dịch đang tiền điện
+lọc các giao dịch đang chuyển cùng ngân hàng
+giao dịch chuyển liên ngân hàng
+lọc các giao dịch đang chuyển liên ngân hàng
+danh sách giao dịch tiền điện
+giao dịch chuyển cùng ngân hàng</t>
+  </si>
+  <si>
+    <t>Liệt kê giao dịch của khách hàng CAT_LHL7
+Xem lịch sử của người dùng do CAT_LHL7
+Sao kê cho người dùng do CAT_LHL7</t>
+  </si>
+  <si>
+    <t>Tìm giao dịch có mã yêu cầu gốc là 376
+Tra soát theo mã yêu cầu gốc 376
+Check mã yêu cầu gốc 376 giúp em</t>
+  </si>
+  <si>
+    <t>Sao kê cho khách hàng chuyển tiền 2028834
+Xem lịch sử của khách hàng chuyển tiền 2028834
+Liệt kê giao dịch của khách hàng 2028834</t>
+  </si>
+  <si>
+    <t>Liệt kê giao dịch của khách hàng 3432313
+Sao kê cho customer information file 3432313
+Xem lịch sử của customer information file 3432313</t>
+  </si>
+  <si>
+    <t>Sao kê cho mã chi nhánh quản lý khách hàng người chuyển TYPE_8JPZ
+Liệt kê giao dịch của khách hàng TYPE_8JPZ
+Xem lịch sử của mã chi nhánh quản lý khách hàng người chuyển TYPE_8JPZ</t>
+  </si>
+  <si>
+    <t>Lọc giao dịch theo hạng hoặc nhóm tài khoản nguồn MODE_042D
+Danh sách giao dịch có hạng hoặc nhóm tài khoản nguồn là MODE_042D</t>
+  </si>
+  <si>
+    <t>danh sách giao dịch nạp thẻ
+giao dịch nạp thẻ
+lọc các giao dịch đang chuyển ra ngoài
+danh sách giao dịch chuyển cùng ngân hàng
+giao dịch chuyển ra ngoài
+lọc các giao dịch đang chuyển cùng ngân hàng
+danh sách giao dịch chuyển ra ngoài
 lọc các giao dịch đang nạp thẻ
-lọc các giao dịch đang chuyển liên ngân hàng
-giao dịch nạp thẻ
-giao dịch chuyển liên ngân hàng</t>
-  </si>
-  <si>
-    <t>giao dịch ứng dụng
-giao dịch máy rút tiền
-lọc các giao dịch đang máy rút tiền
-danh sách giao dịch máy rút tiền
-giao dịch quầy giao dịch
-lọc các giao dịch đang quầy giao dịch
-danh sách giao dịch quầy giao dịch
-danh sách giao dịch ứng dụng
-lọc các giao dịch đang ứng dụng</t>
-  </si>
-  <si>
-    <t>lọc các giao dịch đang chuyển ra ngoài
-lọc các giao dịch đang tiền nước
-danh sách giao dịch chuyển ra ngoài
-danh sách giao dịch nạp tiền điện thoại
-giao dịch nạp tiền điện thoại
-lọc các giao dịch đang nạp tiền điện thoại
-giao dịch tiền nước
-giao dịch chuyển ra ngoài
-danh sách giao dịch tiền nước</t>
-  </si>
-  <si>
-    <t>Liệt kê giao dịch của khách hàng MODE_23ZE
-Sao kê cho người dùng do MODE_23ZE
-Xem lịch sử của người dùng do MODE_23ZE</t>
-  </si>
-  <si>
-    <t>Tra soát theo mã yêu cầu gốc 527
-Check mã yêu cầu gốc 527 giúp em
-Tìm giao dịch có mã yêu cầu gốc là 527</t>
-  </si>
-  <si>
-    <t>Sao kê cho id khách hàng chuyển tiền/người thanh toán. 7187946
-Liệt kê giao dịch của khách hàng 7187946
-Xem lịch sử của id khách hàng chuyển tiền/người thanh toán. 7187946</t>
-  </si>
-  <si>
-    <t>Xem lịch sử của số từ khách hàng 2288395
-Sao kê cho số từ khách hàng 2288395
-Liệt kê giao dịch của khách hàng 2288395</t>
-  </si>
-  <si>
-    <t>Liệt kê giao dịch của khách hàng CAT_EZ0B
-Xem lịch sử của mã chi nhánh quản lý khách hàng người chuyển CAT_EZ0B
-Sao kê cho mã chi nhánh quản lý khách hàng người chuyển CAT_EZ0B</t>
-  </si>
-  <si>
-    <t>Danh sách giao dịch có hạng hoặc nhóm tài khoản nguồn là TYPE_EMH2
-Lọc giao dịch theo hạng hoặc nhóm tài khoản nguồn TYPE_EMH2</t>
-  </si>
-  <si>
-    <t>danh sách giao dịch hóa đơn điện
-giao dịch hóa đơn điện
-giao dịch chuyển cùng ngân hàng
-danh sách giao dịch thanh toán qr
-danh sách giao dịch chuyển cùng ngân hàng
-lọc các giao dịch đang chuyển cùng ngân hàng
-lọc các giao dịch đang thanh toán qr
-giao dịch thanh toán qr
-lọc các giao dịch đang hóa đơn điện</t>
-  </si>
-  <si>
-    <t>Lọc giao dịch theo vnd, usd, eur... đồng
-Danh sách giao dịch có vnd, usd, eur... là đồng</t>
-  </si>
-  <si>
-    <t>Danh sách giao dịch có từ tài khoản tên đầy đủ là MODE_0GR3
-Lọc giao dịch theo từ tài khoản tên đầy đủ MODE_0GR3</t>
-  </si>
-  <si>
-    <t>Xem lịch sử của số đến khách hàng 6501961
-Liệt kê giao dịch của khách hàng 6501961
-Sao kê cho số đến khách hàng 6501961</t>
-  </si>
-  <si>
-    <t>Sao kê cho mã chi nhánh quản lý khách hàng thụ hưởng. MODE_BDKK
-Xem lịch sử của mã chi nhánh quản lý khách hàng thụ hưởng. MODE_BDKK
-Liệt kê giao dịch của khách hàng MODE_BDKK</t>
-  </si>
-  <si>
-    <t>Lọc giao dịch theo đến tài khoản loại tiền đồng
-Danh sách giao dịch có đến tài khoản loại tiền là đồng</t>
-  </si>
-  <si>
-    <t>Tổng sau khi quy đổi tỷ giá nếu có là bao nhiêu?
-Tính tổng sau khi quy đổi tỷ giá nếu có của các giao dịch thành công
-Thống kê sau khi quy đổi tỷ giá nếu có hôm nay</t>
-  </si>
-  <si>
-    <t>Tổng số tiền giao dịch là bao nhiêu?
-Tính tổng số tiền giao dịch của các giao dịch thành công
-Thống kê số tiền giao dịch hôm nay</t>
+giao dịch chuyển cùng ngân hàng</t>
+  </si>
+  <si>
+    <t>Lọc giao dịch theo từ tài khoản loại tiền usd
+Danh sách giao dịch có từ tài khoản loại tiền là usd</t>
+  </si>
+  <si>
+    <t>Lọc giao dịch theo từ tài khoản tên đầy đủ GRP_G299
+Danh sách giao dịch có từ tài khoản tên đầy đủ là GRP_G299</t>
+  </si>
+  <si>
+    <t>Liệt kê giao dịch của khách hàng 5329534
+Xem lịch sử của nếu là chuyển khoản nội bộ 5329534
+Sao kê cho nếu là chuyển khoản nội bộ 5329534</t>
+  </si>
+  <si>
+    <t>Xem lịch sử của đến khách hàng chi nhánh CAT_WOMD
+Sao kê cho đến khách hàng chi nhánh CAT_WOMD
+Liệt kê giao dịch của khách hàng CAT_WOMD</t>
+  </si>
+  <si>
+    <t>Danh sách giao dịch có đến tài khoản loại tiền là đô la
+Lọc giao dịch theo đến tài khoản loại tiền đô la</t>
+  </si>
+  <si>
+    <t>Tổng số tiền thực tế ghi có vào tài khoản nhận là bao nhiêu?
+Tính tổng số tiền thực tế ghi có vào tài khoản nhận của các giao dịch thành công
+Thống kê số tiền thực tế ghi có vào tài khoản nhận hôm nay</t>
+  </si>
+  <si>
+    <t>Tổng số tiền chuyển là bao nhiêu?
+Tính tổng số tiền chuyển của các giao dịch thành công
+Thống kê số tiền chuyển hôm nay</t>
   </si>
   <si>
     <t>Tổng số tiền loại tiền là bao nhiêu?
@@ -541,18 +535,18 @@
 Thống kê số tiền loại tiền hôm nay</t>
   </si>
   <si>
-    <t>Danh sách giao dịch có số tiền lãi suất là 1150000
-Lọc giao dịch theo số tiền lãi suất 1150000</t>
-  </si>
-  <si>
-    <t>Tổng tiền bị giữ là bao nhiêu?
-Tính tổng tiền bị giữ của các giao dịch thành công
-Thống kê tiền bị giữ hôm nay</t>
-  </si>
-  <si>
-    <t>Tra soát theo mã tham chiếu lệnh phong tỏa tiền 5600000
-Tìm giao dịch có mã tham chiếu lệnh phong tỏa tiền là 5600000
-Check mã tham chiếu lệnh phong tỏa tiền 5600000 giúp em</t>
+    <t>Lọc giao dịch theo tỷ giá quy đổi áp dụng cho giao dịch 10000
+Danh sách giao dịch có tỷ giá quy đổi áp dụng cho giao dịch là 10000</t>
+  </si>
+  <si>
+    <t>Tổng block số tiền là bao nhiêu?
+Tính tổng block số tiền của các giao dịch thành công
+Thống kê block số tiền hôm nay</t>
+  </si>
+  <si>
+    <t>Tra soát theo số trạng thái số tiền tham chiếu 42000000
+Check số trạng thái số tiền tham chiếu 42000000 giúp em
+Tìm giao dịch có số trạng thái số tiền tham chiếu là 42000000</t>
   </si>
   <si>
     <t>Tổng phí affect object là bao nhiêu?
@@ -560,376 +554,376 @@
 Thống kê phí affect object hôm nay</t>
   </si>
   <si>
-    <t>Tổng phí dịch vụ là bao nhiêu?
-Tính tổng phí dịch vụ của các giao dịch thành công
-Thống kê phí dịch vụ hôm nay</t>
-  </si>
-  <si>
-    <t>Tổng loại tiền tệ phí. là bao nhiêu?
-Tính tổng loại tiền tệ phí. của các giao dịch thành công
-Thống kê loại tiền tệ phí. hôm nay</t>
-  </si>
-  <si>
-    <t>Tổng nếu loại tiền phí khác loại tiền tài khoản là bao nhiêu?
-Tính tổng nếu loại tiền phí khác loại tiền tài khoản của các giao dịch thành công
-Thống kê nếu loại tiền phí khác loại tiền tài khoản hôm nay</t>
-  </si>
-  <si>
-    <t>Tổng số tiền hoa hồng trả cho đại lý/đối tác là bao nhiêu?
-Tính tổng số tiền hoa hồng trả cho đại lý/đối tác của các giao dịch thành công
-Thống kê số tiền hoa hồng trả cho đại lý/đối tác hôm nay</t>
-  </si>
-  <si>
-    <t>Lọc giao dịch theo hoa hồng loại tiền đô
-Danh sách giao dịch có hoa hồng loại tiền là đô</t>
-  </si>
-  <si>
-    <t>Tra soát theo reference number FT2568230508
-Tìm giao dịch có reference number là FT2568230508
-Check reference number FT2568230508 giúp em</t>
-  </si>
-  <si>
-    <t>Sao kê giao dịch theo yêu cầu thời gian từ ngày 2026-01-31 đến ngày 2026-02-03
-Lọc giao dịch có yêu cầu thời gian trong khoảng 2026-01-31 - 2026-02-03
-Xem lịch sử giao dịch dựa trên yêu cầu thời gian từ 2026-01-31 tới 2026-02-03
-Kiểm tra các giao dịch với yêu cầu thời gian là ngày 2026-01-31</t>
-  </si>
-  <si>
-    <t>danh sách giao dịch mobile app
-giao dịch máy rút tiền
-lọc các giao dịch đang máy rút tiền
-giao dịch i-banking
-danh sách giao dịch máy rút tiền
-danh sách giao dịch i-banking
-giao dịch mobile app
-lọc các giao dịch đang i-banking
-lọc các giao dịch đang mobile app</t>
-  </si>
-  <si>
-    <t>Tra soát theo số giao dịch revert tham chiếu FT5481594855
-Tìm giao dịch có số giao dịch revert tham chiếu là FT5481594855
-Check số giao dịch revert tham chiếu FT5481594855 giúp em</t>
-  </si>
-  <si>
-    <t>Sao kê giao dịch theo response thời gian từ ngày 2025-12-21 đến ngày 2026-02-03
-Lọc giao dịch có response thời gian trong khoảng 2025-12-21 - 2026-02-03
-Xem lịch sử giao dịch dựa trên response thời gian từ 2025-12-21 tới 2026-02-03
-Kiểm tra các giao dịch với response thời gian là ngày 2025-12-21</t>
-  </si>
-  <si>
-    <t>danh sách giao dịch treo
-lọc các giao dịch đang hết hạn
-giao dịch treo
-danh sách giao dịch hết hạn
+    <t>Tổng phí số tiền là bao nhiêu?
+Tính tổng phí số tiền của các giao dịch thành công
+Thống kê phí số tiền hôm nay</t>
+  </si>
+  <si>
+    <t>Tổng phí loại tiền là bao nhiêu?
+Tính tổng phí loại tiền của các giao dịch thành công
+Thống kê phí loại tiền hôm nay</t>
+  </si>
+  <si>
+    <t>Tổng phí số tiền lãi suất là bao nhiêu?
+Tính tổng phí số tiền lãi suất của các giao dịch thành công
+Thống kê phí số tiền lãi suất hôm nay</t>
+  </si>
+  <si>
+    <t>Tổng nếu có là bao nhiêu?
+Tính tổng nếu có của các giao dịch thành công
+Thống kê nếu có hôm nay</t>
+  </si>
+  <si>
+    <t>Lọc giao dịch theo loại tiền tệ hoa hồng đồng
+Danh sách giao dịch có loại tiền tệ hoa hồng là đồng</t>
+  </si>
+  <si>
+    <t>Check số giao dịch tham chiếu FT6987037386 giúp em
+Tìm giao dịch có số giao dịch tham chiếu là FT6987037386
+Tra soát theo số giao dịch tham chiếu FT6987037386</t>
+  </si>
+  <si>
+    <t>Sao kê giao dịch theo yêu cầu thời gian từ ngày 2025-12-10 đến ngày 2026-02-03
+Lọc giao dịch có yêu cầu thời gian trong khoảng 2025-12-10 - 2026-02-03
+Xem lịch sử giao dịch dựa trên yêu cầu thời gian từ 2025-12-10 tới 2026-02-03
+Kiểm tra các giao dịch với yêu cầu thời gian là ngày 2025-12-10</t>
+  </si>
+  <si>
+    <t>giao dịch ứng dụng
+lọc các giao dịch đang ứng dụng
+danh sách giao dịch chi nhánh
+giao dịch tại atm
+danh sách giao dịch ứng dụng
+lọc các giao dịch đang tại atm
+giao dịch chi nhánh
+danh sách giao dịch tại atm
+lọc các giao dịch đang chi nhánh</t>
+  </si>
+  <si>
+    <t>Check số giao dịch revert tham chiếu FT8499827309 giúp em
+Tra soát theo số giao dịch revert tham chiếu FT8499827309
+Tìm giao dịch có số giao dịch revert tham chiếu là FT8499827309</t>
+  </si>
+  <si>
+    <t>Sao kê giao dịch theo trạng thái giờ từ ngày 2025-12-11 đến ngày 2026-02-03
+Lọc giao dịch có trạng thái giờ trong khoảng 2025-12-11 - 2026-02-03
+Xem lịch sử giao dịch dựa trên trạng thái giờ từ 2025-12-11 tới 2026-02-03
+Kiểm tra các giao dịch với trạng thái giờ là ngày 2025-12-11</t>
+  </si>
+  <si>
+    <t>giao dịch thành công
+danh sách giao dịch quá giờ
+lọc các giao dịch đang lỗi
+danh sách giao dịch lỗi
+danh sách giao dịch thành công
+lọc các giao dịch đang quá giờ
+lọc các giao dịch đang thành công
+giao dịch quá giờ
+giao dịch lỗi</t>
+  </si>
+  <si>
+    <t>Sao kê giao dịch theo thời gian duyệt giao dịch từ ngày 2026-01-04 đến ngày 2026-02-03
+Lọc giao dịch có thời gian duyệt giao dịch trong khoảng 2026-01-04 - 2026-02-03
+Xem lịch sử giao dịch dựa trên thời gian duyệt giao dịch từ 2026-01-04 tới 2026-02-03
+Kiểm tra các giao dịch với thời gian duyệt giao dịch là ngày 2026-01-04</t>
+  </si>
+  <si>
+    <t>Sao kê giao dịch theo ngày sản phẩm từ ngày 2025-12-05 đến ngày 2026-02-03
+Lọc giao dịch có ngày sản phẩm trong khoảng 2025-12-05 - 2026-02-03
+Xem lịch sử giao dịch dựa trên ngày sản phẩm từ 2025-12-05 tới 2026-02-03
+Kiểm tra các giao dịch với ngày sản phẩm là ngày 2025-12-05</t>
+  </si>
+  <si>
+    <t>lọc các giao dịch đang đang chờ
+giao dịch thành công
+danh sách giao dịch bị treo
+danh sách giao dịch đang chờ
+danh sách giao dịch thành công
+lọc các giao dịch đang bị treo
+lọc các giao dịch đang thành công
+giao dịch bị treo
+giao dịch đang chờ</t>
+  </si>
+  <si>
+    <t>danh sách giao dịch xử lý
+giao dịch xử lý
+lọc các giao dịch đang xử lý
 giao dịch thành công
 danh sách giao dịch thành công
-lọc các giao dịch đang treo
-giao dịch hết hạn
+lọc các giao dịch đang quá giờ
+danh sách giao dịch quá giờ
+giao dịch quá giờ
 lọc các giao dịch đang thành công</t>
   </si>
   <si>
-    <t>Sao kê giao dịch theo thời gian duyệt giao dịch từ ngày 2026-01-11 đến ngày 2026-02-03
-Lọc giao dịch có thời gian duyệt giao dịch trong khoảng 2026-01-11 - 2026-02-03
-Xem lịch sử giao dịch dựa trên thời gian duyệt giao dịch từ 2026-01-11 tới 2026-02-03
-Kiểm tra các giao dịch với thời gian duyệt giao dịch là ngày 2026-01-11</t>
-  </si>
-  <si>
-    <t>Sao kê giao dịch theo thời gian tạo lệnh. từ ngày 2026-01-29 đến ngày 2026-02-03
-Lọc giao dịch có thời gian tạo lệnh. trong khoảng 2026-01-29 - 2026-02-03
-Xem lịch sử giao dịch dựa trên thời gian tạo lệnh. từ 2026-01-29 tới 2026-02-03
-Kiểm tra các giao dịch với thời gian tạo lệnh. là ngày 2026-01-29</t>
-  </si>
-  <si>
-    <t>danh sách giao dịch hoàn tất
+    <t>Tìm giao dịch có số nội dung tham chiếu là FT4813004409
+Tra soát theo số nội dung tham chiếu FT4813004409
+Check số nội dung tham chiếu FT4813004409 giúp em</t>
+  </si>
+  <si>
+    <t>Tra soát theo số nội dung trạng thái tham chiếu FT0084697698
+Check số nội dung trạng thái tham chiếu FT0084697698 giúp em
+Tìm giao dịch có số nội dung trạng thái tham chiếu là FT0084697698</t>
+  </si>
+  <si>
+    <t>Tìm giao dịch có mã giao dịch tham chiếu cổng thanh toán là FT4410552367
+Check mã giao dịch tham chiếu cổng thanh toán FT4410552367 giúp em
+Tra soát theo mã giao dịch tham chiếu cổng thanh toán FT4410552367</t>
+  </si>
+  <si>
+    <t>lọc các giao dịch đang đang chờ
+danh sách giao dịch hoàn tất
+danh sách giao dịch đang chờ
 giao dịch hoàn tất
-lọc các giao dịch đang hết hạn
-giao dịch treo
-danh sách giao dịch hết hạn
-lọc các giao dịch đang treo
-giao dịch hết hạn
+lọc các giao dịch đang quá giờ
+danh sách giao dịch quá giờ
+giao dịch quá giờ
 lọc các giao dịch đang hoàn tất
-danh sách giao dịch treo</t>
-  </si>
-  <si>
-    <t>danh sách giao dịch thất bại
-danh sách giao dịch hoàn tất
-giao dịch hoàn tất
-lọc các giao dịch đang đang chờ
-danh sách giao dịch đang chờ
-giao dịch đang chờ
-lọc các giao dịch đang hoàn tất
-giao dịch thất bại
-lọc các giao dịch đang thất bại</t>
-  </si>
-  <si>
-    <t>Tra soát theo ft id FT5957913046
-Check ft id FT5957913046 giúp em
-Tìm giao dịch có ft id là FT5957913046</t>
-  </si>
-  <si>
-    <t>Tra soát theo số core revert tham chiếu FT8888220381
-Check số core revert tham chiếu FT8888220381 giúp em
-Tìm giao dịch có số core revert tham chiếu là FT8888220381</t>
-  </si>
-  <si>
-    <t>Check mã giao dịch tham chiếu tại cổng thanh toán. FT6057999846 giúp em
-Tra soát theo mã giao dịch tham chiếu tại cổng thanh toán. FT6057999846
-Tìm giao dịch có mã giao dịch tham chiếu tại cổng thanh toán. là FT6057999846</t>
-  </si>
-  <si>
-    <t>giao dịch lỗi
-danh sách giao dịch xử lý
-lọc các giao dịch đang lỗi
-giao dịch thành công
-danh sách giao dịch thành công
-giao dịch xử lý
-lọc các giao dịch đang xử lý
-danh sách giao dịch lỗi
-lọc các giao dịch đang thành công</t>
-  </si>
-  <si>
-    <t>Liệt kê giao dịch của khách hàng chuyển cùng ngân hàng
-Xem lịch sử của mã hóa đơn khách hàng chuyển cùng ngân hàng
-Sao kê cho mã hóa đơn khách hàng chuyển cùng ngân hàng</t>
+giao dịch đang chờ</t>
+  </si>
+  <si>
+    <t>Liệt kê giao dịch của khách hàng chuyển ra ngoài
+Xem lịch sử của số hóa đơn khách hàng chuyển ra ngoài
+Sao kê cho số hóa đơn khách hàng chuyển ra ngoài</t>
   </si>
   <si>
     <t>giao dịch napas 247
-lọc các giao dịch đang chuyển ra ngoài
-giao dịch hóa đơn nước
-danh sách giao dịch chuyển ra ngoài
-danh sách giao dịch hóa đơn nước
-lọc các giao dịch đang hóa đơn nước
 lọc các giao dịch đang napas 247
-giao dịch chuyển ra ngoài
-danh sách giao dịch napas 247</t>
-  </si>
-  <si>
-    <t>Danh sách giao dịch có loại tiền tệ hóa đơn là đô la
-Lọc giao dịch theo loại tiền tệ hóa đơn đô la</t>
-  </si>
-  <si>
-    <t>Sao kê giao dịch theo ngày hóa đơn từ từ ngày 2026-01-24 đến ngày 2026-02-03
-Lọc giao dịch có ngày hóa đơn từ trong khoảng 2026-01-24 - 2026-02-03
-Xem lịch sử giao dịch dựa trên ngày hóa đơn từ từ 2026-01-24 tới 2026-02-03
-Kiểm tra các giao dịch với ngày hóa đơn từ là ngày 2026-01-24</t>
-  </si>
-  <si>
-    <t>Sao kê giao dịch theo ngày hóa đơn đến từ ngày 2025-12-28 đến ngày 2026-02-03
-Lọc giao dịch có ngày hóa đơn đến trong khoảng 2025-12-28 - 2026-02-03
-Xem lịch sử giao dịch dựa trên ngày hóa đơn đến từ 2025-12-28 tới 2026-02-03
-Kiểm tra các giao dịch với ngày hóa đơn đến là ngày 2025-12-28</t>
-  </si>
-  <si>
-    <t>Sao kê giao dịch theo thời gian bản ghi chèn vào cơ sở từ ngày 2025-12-13 đến ngày 2026-02-03
-Lọc giao dịch có thời gian bản ghi chèn vào cơ sở trong khoảng 2025-12-13 - 2026-02-03
-Xem lịch sử giao dịch dựa trên thời gian bản ghi chèn vào cơ sở từ 2025-12-13 tới 2026-02-03
-Kiểm tra các giao dịch với thời gian bản ghi chèn vào cơ sở là ngày 2025-12-13</t>
-  </si>
-  <si>
-    <t>Sao kê giao dịch theo finish thời gian từ ngày 2026-01-06 đến ngày 2026-02-03
-Lọc giao dịch có finish thời gian trong khoảng 2026-01-06 - 2026-02-03
-Xem lịch sử giao dịch dựa trên finish thời gian từ 2026-01-06 tới 2026-02-03
-Kiểm tra các giao dịch với finish thời gian là ngày 2026-01-06</t>
-  </si>
-  <si>
-    <t>Tổng discount số tiền là bao nhiêu?
-Tính tổng discount số tiền của các giao dịch thành công
-Thống kê discount số tiền hôm nay</t>
-  </si>
-  <si>
-    <t>Tổng số tiền người dùng nhập vào ban đầu là bao nhiêu?
-Tính tổng số tiền người dùng nhập vào ban đầu của các giao dịch thành công
-Thống kê số tiền người dùng nhập vào ban đầu hôm nay</t>
-  </si>
-  <si>
-    <t>Sao kê giao dịch theo thời gian tiền về từ ngày 2026-01-11 đến ngày 2026-02-03
-Lọc giao dịch có thời gian tiền về trong khoảng 2026-01-11 - 2026-02-03
-Xem lịch sử giao dịch dựa trên thời gian tiền về từ 2026-01-11 tới 2026-02-03
-Kiểm tra các giao dịch với thời gian tiền về là ngày 2026-01-11</t>
-  </si>
-  <si>
-    <t>Tổng thuế vat là bao nhiêu?
-Tính tổng thuế vat của các giao dịch thành công
-Thống kê thuế vat hôm nay</t>
-  </si>
-  <si>
-    <t>Tổng số tiền chiết khấu do đối tác tài trợ. là bao nhiêu?
-Tính tổng số tiền chiết khấu do đối tác tài trợ. của các giao dịch thành công
-Thống kê số tiền chiết khấu do đối tác tài trợ. hôm nay</t>
-  </si>
-  <si>
-    <t>lọc các giao dịch đang tiền điện
-lọc các giao dịch đang chuyển ra ngoài
-danh sách giao dịch chuyển ra ngoài
-lọc các giao dịch đang chuyển nhanh
-giao dịch chuyển nhanh
+danh sách giao dịch nạp tiền điện thoại
+lọc các giao dịch đang nạp tiền điện thoại
+giao dịch tiền nước
+giao dịch nạp tiền điện thoại
+lọc các giao dịch đang tiền nước
+danh sách giao dịch napas 247
+danh sách giao dịch tiền nước</t>
+  </si>
+  <si>
+    <t>Lọc giao dịch theo loại tiền tệ hóa đơn vnđ
+Danh sách giao dịch có loại tiền tệ hóa đơn là vnđ</t>
+  </si>
+  <si>
+    <t>Sao kê giao dịch theo ngày bắt đầu kỳ cước hóa đơn từ ngày 2026-01-18 đến ngày 2026-02-03
+Lọc giao dịch có ngày bắt đầu kỳ cước hóa đơn trong khoảng 2026-01-18 - 2026-02-03
+Xem lịch sử giao dịch dựa trên ngày bắt đầu kỳ cước hóa đơn từ 2026-01-18 tới 2026-02-03
+Kiểm tra các giao dịch với ngày bắt đầu kỳ cước hóa đơn là ngày 2026-01-18</t>
+  </si>
+  <si>
+    <t>Sao kê giao dịch theo ngày hóa đơn đến từ ngày 2025-12-14 đến ngày 2026-02-03
+Lọc giao dịch có ngày hóa đơn đến trong khoảng 2025-12-14 - 2026-02-03
+Xem lịch sử giao dịch dựa trên ngày hóa đơn đến từ 2025-12-14 tới 2026-02-03
+Kiểm tra các giao dịch với ngày hóa đơn đến là ngày 2025-12-14</t>
+  </si>
+  <si>
+    <t>Sao kê giao dịch theo insert thời gian từ ngày 2025-12-06 đến ngày 2026-02-03
+Lọc giao dịch có insert thời gian trong khoảng 2025-12-06 - 2026-02-03
+Xem lịch sử giao dịch dựa trên insert thời gian từ 2025-12-06 tới 2026-02-03
+Kiểm tra các giao dịch với insert thời gian là ngày 2025-12-06</t>
+  </si>
+  <si>
+    <t>Sao kê giao dịch theo thời gian kết thúc từ ngày 2025-12-10 đến ngày 2026-02-03
+Lọc giao dịch có thời gian kết thúc trong khoảng 2025-12-10 - 2026-02-03
+Xem lịch sử giao dịch dựa trên thời gian kết thúc từ 2025-12-10 tới 2026-02-03
+Kiểm tra các giao dịch với thời gian kết thúc là ngày 2025-12-10</t>
+  </si>
+  <si>
+    <t>Tổng khuyến mãi là bao nhiêu?
+Tính tổng khuyến mãi của các giao dịch thành công
+Thống kê khuyến mãi hôm nay</t>
+  </si>
+  <si>
+    <t>Tổng nội dung số tiền là bao nhiêu?
+Tính tổng nội dung số tiền của các giao dịch thành công
+Thống kê nội dung số tiền hôm nay</t>
+  </si>
+  <si>
+    <t>Sao kê giao dịch theo receive thời gian từ ngày 2026-01-17 đến ngày 2026-02-03
+Lọc giao dịch có receive thời gian trong khoảng 2026-01-17 - 2026-02-03
+Xem lịch sử giao dịch dựa trên receive thời gian từ 2026-01-17 tới 2026-02-03
+Kiểm tra các giao dịch với receive thời gian là ngày 2026-01-17</t>
+  </si>
+  <si>
+    <t>Tổng thường tính trên phí dịch vụ là bao nhiêu?
+Tính tổng thường tính trên phí dịch vụ của các giao dịch thành công
+Thống kê thường tính trên phí dịch vụ hôm nay</t>
+  </si>
+  <si>
+    <t>Tổng chiết khấu đối tác là bao nhiêu?
+Tính tổng chiết khấu đối tác của các giao dịch thành công
+Thống kê chiết khấu đối tác hôm nay</t>
+  </si>
+  <si>
+    <t>danh sách giao dịch nạp thẻ
+giao dịch nạp thẻ
 giao dịch tiền điện
-danh sách giao dịch chuyển nhanh
-giao dịch chuyển ra ngoài
-danh sách giao dịch tiền điện</t>
-  </si>
-  <si>
-    <t>Liệt kê giao dịch của khách hàng 5921529
-Xem lịch sử của mã khách hàng tác nghiệp số 5921529
-Sao kê cho mã khách hàng tác nghiệp số 5921529</t>
-  </si>
-  <si>
-    <t>Tổng giá trị tiền ghi trên hóa đơn cần thanh toán. là bao nhiêu?
-Tính tổng giá trị tiền ghi trên hóa đơn cần thanh toán. của các giao dịch thành công
-Thống kê giá trị tiền ghi trên hóa đơn cần thanh toán. hôm nay</t>
-  </si>
-  <si>
-    <t>Sao kê cho tương tự from_cust_no nhưng thường định danh core banking 3052922
-Liệt kê giao dịch của khách hàng 3052922
-Xem lịch sử của tương tự from_cust_no nhưng thường định danh core banking 3052922</t>
-  </si>
-  <si>
-    <t>giao dịch nạp tiền điện thoại trên 710000
-Tìm các giao dịch nạp tiền điện thoại &gt; 710000</t>
-  </si>
-  <si>
-    <t>khóa chính, khóa chính là mã định danh duy nhất mỗi bản ghi giao dịch trong này, số tham chiếu, primary key, số ref, số bút toán, mã tham chiếu</t>
-  </si>
-  <si>
-    <t>mã định danh giao dịch theo nghiệp vụ phân biệt các giao dịch với nhau, có thể tra soát, số giao dịch, số tham chiếu, mã định danh giao dịch theo nghiệp vụ, phân biệt các giao dịch với nhau, mã giao dịch, mã lệnh</t>
-  </si>
-  <si>
-    <t>mã lệnh cha, giao dịch gốc, giao dịch cha, số parent, id giao dịch cha dùng trong trường hợp giao dịch này là giao dịch con hoặc một bước trong chuỗi giao dịch phức tạp, mã parent, id giao dịch cha, trường hợp giao dịch này giao dịch con hoặc một bước chuỗi giao dịch phức tạp.</t>
-  </si>
-  <si>
-    <t>thời gian, lịch sử, thời điểm chính xác giao dịch phát sinh.</t>
-  </si>
-  <si>
-    <t>loại giao dịch hoặc nhóm giao dịch, loại giao dịch, loại giao dịch chi tiết hoặc mô tả nhóm giao dịch.</t>
-  </si>
-  <si>
-    <t>nguồn nhận, kênh người nhận, kênh nhận, kênh tiếp nhận giao dịch, ví dụ: mobile app, internet banking, atm, counter</t>
-  </si>
-  <si>
-    <t>stak người dùng loại do, loại người dùng tác nghiệp, loại tác nghiệp, thường cho nhân viên vận hành/digital officer</t>
-  </si>
-  <si>
-    <t>người dùng do, tên hoặc mã nhân viên vận hành/hỗ trợ liên quan đến giao dịch này, nếu có</t>
-  </si>
-  <si>
-    <t>mã yêu cầu gốc, mã gốc yêu cầu, số gốc yêu cầu, dùng cho các giao dịch hoàn tiền, hủy hoặc đảo giao dịch tham chiếu lại giao dịch cũ</t>
-  </si>
-  <si>
-    <t>id khách hàng chuyển tiền/người thanh toán., số từ khách hàng, mã từ khách hàng, id khách hàng người chuyển tiền/người thanh toán</t>
-  </si>
-  <si>
-    <t>số từ khách hàng, mã cif, mã cif hoặc mã khách hàng người chuyển, customer information file</t>
-  </si>
-  <si>
-    <t>mã chi nhánh quản lý khách hàng người chuyển, mã chi nhánh quản lý khách hàng chuyển., từ khách hàng chi nhánh</t>
-  </si>
-  <si>
-    <t>hạng hoặc nhóm tài khoản nguồn, loại từ tài khoản, ví dụ: dda - thanh toán, fd - tiết kiệm</t>
-  </si>
-  <si>
-    <t>loại tài khoản nguồn, loại từ tài khoản, loại tài khoản nguồn chi tiết.</t>
-  </si>
-  <si>
-    <t>vnd, usd, eur..., loại tiền tệ tài khoản nguồn, từ tài khoản loại tiền</t>
-  </si>
-  <si>
-    <t>từ tài khoản tên đầy đủ, tên đầy đủ chủ tài khoản nguồn., tên đầy đủ chủ tài khoản nguồn</t>
-  </si>
-  <si>
-    <t>số đến khách hàng, mã khách hàng thụ hưởng, nếu chuyển khoản nội bộ, mã khách hàng người thụ hưởng</t>
-  </si>
-  <si>
-    <t>mã chi nhánh quản lý khách hàng thụ hưởng., đến khách hàng chi nhánh, mã chi nhánh quản lý khách hàng thụ hưởng</t>
-  </si>
-  <si>
-    <t>đến tài khoản loại tiền, loại tiền tệ tài khoản đích., loại tiền tệ tài khoản đích</t>
+lọc các giao dịch đang tiền điện
+giao dịch tiền nước
+lọc các giao dịch đang tiền nước
+lọc các giao dịch đang nạp thẻ
+danh sách giao dịch tiền điện
+danh sách giao dịch tiền nước</t>
+  </si>
+  <si>
+    <t>Liệt kê giao dịch của khách hàng 1206327
+Xem lịch sử của khách hàng số do 1206327
+Sao kê cho khách hàng số do 1206327</t>
+  </si>
+  <si>
+    <t>Tổng giá trị tiền ghi trên hóa đơn cần thanh toán là bao nhiêu?
+Tính tổng giá trị tiền ghi trên hóa đơn cần thanh toán của các giao dịch thành công
+Thống kê giá trị tiền ghi trên hóa đơn cần thanh toán hôm nay</t>
+  </si>
+  <si>
+    <t>Liệt kê giao dịch của khách hàng 9899391
+Sao kê cho số từ mã khách hàng 9899391
+Xem lịch sử của số từ mã khách hàng 9899391</t>
+  </si>
+  <si>
+    <t>giao dịch hóa đơn điện trên 2500000
+Tìm các giao dịch hóa đơn điện &gt; 2500000</t>
+  </si>
+  <si>
+    <t>số bút toán, mã tham chiếu, mã định danh duy nhất cho mỗi bản ghi giao dịch này, số ref, primary key, khóa chính là mã định danh duy nhất mỗi bản ghi giao dịch trong này, số tham chiếu</t>
+  </si>
+  <si>
+    <t>phân biệt các giao dịch với nhau, mã định danh giao dịch theo nghiệp vụ, mã lệnh, mã giao dịch, số giao dịch, có thể dùng để tra soát, số tham chiếu, mã định danh giao dịch theo nghiệp vụ phân biệt các giao dịch với nhau</t>
+  </si>
+  <si>
+    <t>số parent, mã lệnh cha, giao dịch gốc, mã parent, id giao dịch cha dùng trong trường hợp giao dịch này là giao dịch con hoặc một bước trong chuỗi giao dịch phức tạp, hợp giao dịch này giao dịch con hoặc một bước chuỗi giao dịch phức tạp, giao dịch cha</t>
+  </si>
+  <si>
+    <t>thời gian, lịch sử, thời điểm chính xác giao dịch phát sinh</t>
+  </si>
+  <si>
+    <t>loại giao dịch chi tiết hoặc mô tả nhóm giao dịch, loại giao dịch hoặc nhóm giao dịch, loại giao dịch</t>
+  </si>
+  <si>
+    <t>kênh tiếp nhận giao dịch, mobile app, kênh nhận, internet banking, nguồn nhận, kênh người nhận, atm, counter</t>
+  </si>
+  <si>
+    <t>loại người dùng tác nghiệp, thường dùng cho nhân viên vận hành/digital officer, trạng thái người dùng loại nội dung, stak người dùng loại do, loại tác nghiệp</t>
+  </si>
+  <si>
+    <t>người dùng do, nếu có, tên hoặc mã nhân viên vận hành, người dùng nội dung, tên hoặc mã nhân viên vận hành/hỗ trợ liên quan đến giao dịch này, hỗ trợ liên quan đến giao dịch này</t>
+  </si>
+  <si>
+    <t>mã yêu cầu gốc, dùng cho các giao dịch hoàn tiền, mã gốc yêu cầu, số gốc yêu cầu, hủy hoặc đảo giao dịch để tham chiếu lại giao dịch cũ</t>
+  </si>
+  <si>
+    <t>khách hàng chuyển tiền, mã từ khách hàng, thanh toán, số từ khách hàng, id khách hàng người chuyển tiền/người thanh toán</t>
+  </si>
+  <si>
+    <t>customer information file, mã cif hoặc mã khách hàng chuyển, mã cif hoặc mã khách hàng người chuyển, số từ khách hàng</t>
+  </si>
+  <si>
+    <t>mã chi nhánh quản lý khách hàng người chuyển, mã chi nhánh quản lý khách hàng chuyển, từ khách hàng chi nhánh</t>
+  </si>
+  <si>
+    <t>hạng hoặc nhóm tài khoản nguồn, loại từ tài khoản, dda - thanh toán, fd - tiết kiệm</t>
+  </si>
+  <si>
+    <t>loại từ tài khoản, loại tài khoản nguồn, loại tài khoản nguồn chi tiết</t>
+  </si>
+  <si>
+    <t>từ tài khoản loại tiền, loại tiền tệ tài khoản nguồn, eur..., usd, vnd</t>
+  </si>
+  <si>
+    <t>từ tài khoản tên đầy đủ, tên đầy đủ chủ tài khoản nguồn</t>
+  </si>
+  <si>
+    <t>nếu là chuyển khoản nội bộ, mã khách hàng thụ hưởng, mã khách hàng người thụ hưởng, số đến khách hàng</t>
+  </si>
+  <si>
+    <t>đến khách hàng chi nhánh, mã chi nhánh quản lý khách hàng thụ hưởng</t>
+  </si>
+  <si>
+    <t>đến tài khoản loại tiền, loại tiền tệ tài khoản đích</t>
   </si>
   <si>
     <t>tổng, thống kê</t>
   </si>
   <si>
-    <t>số tiền lãi suất, tỷ giá quy đổi áp dụng giao dịch, tỷ giá quy đổi được áp dụng cho giao dịch, nếu chuyển đổi tiền tệ</t>
-  </si>
-  <si>
-    <t>mã tham chiếu lệnh phong tỏa tiền, mã tham chiếu lệnh phong tỏa tiền., số block số tiền tham chiếu</t>
-  </si>
-  <si>
-    <t>hoa hồng loại tiền, loại tiền tệ hoa hồng., loại tiền tệ hoa hồng</t>
-  </si>
-  <si>
-    <t>reference number, số tham chiếu giao dịch, số tham chiếu giao dịch thường in lên biên lai hoặc tra cứu, số giao dịch tham chiếu</t>
+    <t>tỷ giá quy đổi áp dụng cho giao dịch, nếu chuyển đổi tiền tệ, tỷ giá quy đổi áp dụng giao dịch, số tiền lãi suất</t>
+  </si>
+  <si>
+    <t>số trạng thái số tiền tham chiếu, mã tham chiếu lệnh phong tỏa tiền, số block số tiền tham chiếu</t>
+  </si>
+  <si>
+    <t>loại tiền tệ hoa hồng, hoa hồng loại tiền</t>
+  </si>
+  <si>
+    <t>số giao dịch tham chiếu, số tham chiếu giao dịch, số tham chiếu giao dịch thường in lên biên lai hoặc tra cứu, thường in lên biên lai hoặc tra cứu, reference number</t>
   </si>
   <si>
     <t>thời gian, lịch sử, yêu cầu thời gian</t>
   </si>
   <si>
-    <t>yêu cầu kênh, kênh gửi yêu cầu, tương tự channel_receiver</t>
-  </si>
-  <si>
-    <t>số giao dịch revert tham chiếu, số tham chiếu giao dịch hoàn tiền/đảo ngược, nếu giao dịch này giao dịch hoàn</t>
-  </si>
-  <si>
-    <t>thời gian, lịch sử, response thời gian</t>
-  </si>
-  <si>
-    <t>trạng thái response, trạng thái phản hồi ngắn gọn, ví dụ: s - success, f - fail</t>
+    <t>tương tự channel_receiver, kênh gửi yêu cầu, yêu cầu kênh</t>
+  </si>
+  <si>
+    <t>số giao dịch revert tham chiếu, số tham chiếu giao dịch hoàn tiền, số tham chiếu giao dịch hoàn tiền/đảo ngược, đảo ngược, số giao dịch trạng thái tham chiếu, nếu giao dịch này là giao dịch hoàn</t>
+  </si>
+  <si>
+    <t>thời gian, lịch sử, trạng thái giờ</t>
+  </si>
+  <si>
+    <t>s - success, f - fail, trạng thái phản hồi ngắn gọn, trạng thái response, trạng thái trạng thái</t>
   </si>
   <si>
     <t>thời gian, lịch sử, thời gian duyệt giao dịch</t>
   </si>
   <si>
-    <t>thời gian, lịch sử, thời gian tạo lệnh.</t>
-  </si>
-  <si>
-    <t>trạng thái phê duyệt, kết quả duyệt, ví dụ: a - approved, r - rejected, p - pending</t>
-  </si>
-  <si>
-    <t>trạng thái cuối cùng giao dịch, thành công/thất bại/chờ xử lý/timeout, trạng thái giao dịch</t>
-  </si>
-  <si>
-    <t>ft id, số bút toán, số bút toán sinh ra trong core banking, số core tham chiếu</t>
-  </si>
-  <si>
-    <t>số core revert tham chiếu, số bút toán đảo trong core banking, nếu có, số bút toán đảo core banking</t>
-  </si>
-  <si>
-    <t>mã giao dịch tham chiếu tại cổng thanh toán., mã giao dịch tham chiếu cổng thanh toán, số thanh toán tham chiếu</t>
-  </si>
-  <si>
-    <t>trạng thái trả từ cổng thanh toán, trạng thái trả về từ cổng thanh toán., trạng thái thanh toán</t>
-  </si>
-  <si>
-    <t>mã hóa đơn khách hàng, số hóa đơn khách hàng, ví dụ: mã danh bộ nước, mã khách hàng điện lực, mã khách hàng trên hóa đơn</t>
-  </si>
-  <si>
-    <t>loại hóa đơn, mã bill, điện, nước, internet, truyền hình...</t>
-  </si>
-  <si>
-    <t>loại tiền tệ hóa đơn, hóa đơn loại tiền, loại tiền tệ hóa đơn.</t>
-  </si>
-  <si>
-    <t>thời gian, lịch sử, ngày hóa đơn từ</t>
+    <t>thời gian, lịch sử, ngày sản phẩm</t>
+  </si>
+  <si>
+    <t>kết quả duyệt, p - pending, a - approved, trạng thái phê duyệt, phê duyệt trạng thái, r - rejected</t>
+  </si>
+  <si>
+    <t>trạng thái cuối cùng giao dịch, trạng thái giao dịch, thành công/thất bại/chờ xử lý/timeout, giao dịch trạng thái</t>
+  </si>
+  <si>
+    <t>số nội dung tham chiếu, số bút toán sinh ra trong core banking, số bút toán sinh ra core banking, số core tham chiếu, ft id</t>
+  </si>
+  <si>
+    <t>số nội dung trạng thái tham chiếu, số bút toán đảo core banking, số core revert tham chiếu, nếu có, số bút toán đảo trong core banking</t>
+  </si>
+  <si>
+    <t>mã giao dịch tham chiếu cổng thanh toán, số thanh toán tham chiếu</t>
+  </si>
+  <si>
+    <t>trạng thái trả về từ cổng thanh toán, trạng thái trả từ cổng thanh toán, thanh toán trạng thái, trạng thái thanh toán</t>
+  </si>
+  <si>
+    <t>số hóa đơn khách hàng, mã danh bộ nước, mã khách hàng trên hóa đơn, mã hóa đơn khách hàng, mã khách hàng điện lực</t>
+  </si>
+  <si>
+    <t>loại hóa đơn, internet, truyền hình..., nước, điện, mã bill</t>
+  </si>
+  <si>
+    <t>loại tiền tệ hóa đơn, hóa đơn loại tiền</t>
+  </si>
+  <si>
+    <t>thời gian, lịch sử, ngày bắt đầu kỳ cước hóa đơn</t>
   </si>
   <si>
     <t>thời gian, lịch sử, ngày hóa đơn đến</t>
   </si>
   <si>
-    <t>thời gian, lịch sử, thời gian bản ghi chèn vào cơ sở</t>
-  </si>
-  <si>
-    <t>thời gian, lịch sử, finish thời gian</t>
-  </si>
-  <si>
-    <t>thời gian, lịch sử, thời gian tiền về</t>
-  </si>
-  <si>
-    <t>loại nguồn tiền, ví dụ: account - tài khoản thanh toán, card - thẻ, ewallet - ví, loại nguồn</t>
-  </si>
-  <si>
-    <t>mã khách hàng tác nghiệp số, khách hàng số do, digital operation</t>
-  </si>
-  <si>
-    <t>tương tự from_cust_no nhưng thường định danh core banking, mã cif người chuyển, số từ mã khách hàng, mã cif, customer information file, số từ số khách hàng</t>
+    <t>thời gian, lịch sử, insert thời gian</t>
+  </si>
+  <si>
+    <t>thời gian, lịch sử, thời gian kết thúc</t>
+  </si>
+  <si>
+    <t>thời gian, lịch sử, receive thời gian</t>
+  </si>
+  <si>
+    <t>ewallet - ví, loại nguồn, card - thẻ, loại nguồn tiền, account - tài khoản thanh toán</t>
+  </si>
+  <si>
+    <t>khách hàng số do, mã khách hàng tác nghiệp số, khách hàng số nội dung, digital operation</t>
+  </si>
+  <si>
+    <t>số từ mã khách hàng, số từ số khách hàng, số từ khách hàng, customer information file, mã cif người chuyển, tương tự from_cust_no nhưng thường dùng định danh core banking, mã cif chuyển</t>
   </si>
   <si>
     <t>lọc nâng cao</t>
@@ -1124,8 +1118,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1177,13 +1171,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1191,21 +1182,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1243,7 +1226,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1277,7 +1260,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1312,10 +1294,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1488,14 +1469,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E63"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="5" width="39.07421875" style="2" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1512,1057 +1490,1057 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>129</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>191</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>192</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="102" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>131</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>193</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="160.30000000000001" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>132</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>194</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>133</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>195</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>134</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>196</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>135</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>197</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>136</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>198</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" t="s">
         <v>137</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>199</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>138</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
         <v>200</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" t="s">
         <v>139</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" t="s">
         <v>201</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s">
         <v>140</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" t="s">
         <v>202</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" t="s">
         <v>203</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" t="s">
         <v>80</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s">
         <v>142</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" t="s">
         <v>204</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" t="s">
         <v>205</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" t="s">
         <v>82</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" t="s">
         <v>206</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s">
         <v>145</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" t="s">
         <v>207</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s">
         <v>146</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" t="s">
         <v>208</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" t="s">
         <v>209</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" t="s">
         <v>210</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" t="s">
         <v>149</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" t="s">
         <v>210</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" t="s">
         <v>150</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" t="s">
         <v>210</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" t="s">
         <v>151</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" t="s">
         <v>211</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" t="s">
         <v>90</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" t="s">
         <v>152</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" t="s">
         <v>210</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" t="s">
         <v>91</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" t="s">
         <v>153</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" t="s">
         <v>212</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" t="s">
         <v>210</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" t="s">
         <v>93</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" t="s">
         <v>155</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" t="s">
         <v>210</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" t="s">
         <v>156</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" t="s">
         <v>210</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A30" s="2" t="s">
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" t="s">
         <v>95</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" t="s">
         <v>157</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" t="s">
         <v>210</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A31" s="2" t="s">
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" t="s">
         <v>96</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" t="s">
         <v>158</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" t="s">
         <v>210</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" t="s">
         <v>159</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" t="s">
         <v>213</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" t="s">
         <v>98</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" t="s">
         <v>160</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" t="s">
         <v>214</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="116.6" x14ac:dyDescent="0.4">
-      <c r="A34" s="2" t="s">
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" t="s">
         <v>99</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" t="s">
         <v>161</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" t="s">
         <v>215</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" t="s">
         <v>100</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" t="s">
         <v>162</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" t="s">
         <v>216</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" t="s">
         <v>101</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" t="s">
         <v>163</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" t="s">
         <v>217</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="116.6" x14ac:dyDescent="0.4">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" t="s">
         <v>102</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" t="s">
         <v>164</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" t="s">
         <v>218</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
-      <c r="A38" s="2" t="s">
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" t="s">
         <v>103</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" t="s">
         <v>165</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" t="s">
         <v>219</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="116.6" x14ac:dyDescent="0.4">
-      <c r="A39" s="2" t="s">
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" t="s">
         <v>104</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" t="s">
         <v>166</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" t="s">
         <v>220</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="116.6" x14ac:dyDescent="0.4">
-      <c r="A40" s="2" t="s">
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" t="s">
         <v>167</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" t="s">
         <v>221</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
-      <c r="A41" s="2" t="s">
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" t="s">
         <v>168</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" t="s">
         <v>222</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
-      <c r="A42" s="2" t="s">
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" t="s">
         <v>107</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" t="s">
         <v>169</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" t="s">
         <v>223</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A43" s="2" t="s">
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" t="s">
         <v>108</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" t="s">
         <v>170</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" t="s">
         <v>224</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A44" s="2" t="s">
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" t="s">
         <v>109</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" t="s">
         <v>171</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" t="s">
         <v>225</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A45" s="2" t="s">
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" t="s">
         <v>110</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" t="s">
         <v>172</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" t="s">
         <v>226</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
-      <c r="A46" s="2" t="s">
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" t="s">
         <v>111</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" t="s">
         <v>173</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" t="s">
         <v>227</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A47" s="2" t="s">
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" t="s">
         <v>112</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" t="s">
         <v>174</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" t="s">
         <v>228</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
-      <c r="A48" s="2" t="s">
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" t="s">
         <v>113</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" t="s">
         <v>175</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" t="s">
         <v>229</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A49" s="2" t="s">
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" t="s">
         <v>114</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" t="s">
         <v>176</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" t="s">
         <v>230</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="116.6" x14ac:dyDescent="0.4">
-      <c r="A50" s="2" t="s">
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" t="s">
         <v>115</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" t="s">
         <v>177</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" t="s">
         <v>231</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="116.6" x14ac:dyDescent="0.4">
-      <c r="A51" s="2" t="s">
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" t="s">
         <v>116</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" t="s">
         <v>178</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" t="s">
         <v>232</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="145.75" x14ac:dyDescent="0.4">
-      <c r="A52" s="2" t="s">
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" t="s">
         <v>117</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" t="s">
         <v>179</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" t="s">
         <v>233</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="116.6" x14ac:dyDescent="0.4">
-      <c r="A53" s="2" t="s">
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" t="s">
         <v>118</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" t="s">
         <v>180</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" t="s">
         <v>234</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E53" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A54" s="2" t="s">
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" t="s">
         <v>119</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" t="s">
         <v>181</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" t="s">
         <v>210</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E54" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A55" s="2" t="s">
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" t="s">
         <v>120</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" t="s">
         <v>182</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" t="s">
         <v>210</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E55" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="116.6" x14ac:dyDescent="0.4">
-      <c r="A56" s="2" t="s">
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" t="s">
         <v>121</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" t="s">
         <v>183</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" t="s">
         <v>235</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A57" s="2" t="s">
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" t="s">
         <v>122</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" t="s">
         <v>184</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" t="s">
         <v>210</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E57" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A58" s="2" t="s">
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
         <v>61</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" t="s">
         <v>123</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" t="s">
         <v>185</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" t="s">
         <v>210</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E58" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="131.15" x14ac:dyDescent="0.4">
-      <c r="A59" s="2" t="s">
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
         <v>62</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" t="s">
         <v>124</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" t="s">
         <v>186</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" t="s">
         <v>236</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E59" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
-      <c r="A60" s="2" t="s">
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
         <v>63</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" t="s">
         <v>125</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" t="s">
         <v>187</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" t="s">
         <v>237</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E60" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A61" s="2" t="s">
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
         <v>64</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" t="s">
         <v>126</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" t="s">
         <v>188</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" t="s">
         <v>210</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E61" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A62" s="2" t="s">
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
         <v>65</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" t="s">
         <v>127</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" t="s">
         <v>189</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" t="s">
         <v>238</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="E62" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="58.3" x14ac:dyDescent="0.4">
-      <c r="A63" s="2" t="s">
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
         <v>66</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" t="s">
         <v>128</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" t="s">
         <v>190</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D63" t="s">
         <v>239</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="E63" t="s">
         <v>301</v>
       </c>
     </row>
